--- a/results/calibration/calibration_validation.xlsx
+++ b/results/calibration/calibration_validation.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://burnetinstitute.sharepoint.com/sites/WG-Modelling-HCVvaccinemodel/Shared Documents/HCV vaccine model/HCV vaccine model/results/calibration/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_01939EEA8DB96EA4AAE033729CF68663F075FB5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E1DF21-2750-42F3-A4A2-938F36D818C7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Countries outcomes" sheetId="1" r:id="rId1"/>
     <sheet name="Countries inci validation" sheetId="2" r:id="rId2"/>
     <sheet name="Plot data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="568">
   <si>
     <t>Country</t>
   </si>
@@ -1305,9 +1299,6 @@
     <t>3,872</t>
   </si>
   <si>
-    <t>3,499</t>
-  </si>
-  <si>
     <t>3,253</t>
   </si>
   <si>
@@ -1329,9 +1320,6 @@
     <t>784</t>
   </si>
   <si>
-    <t>2,879</t>
-  </si>
-  <si>
     <t>13,876</t>
   </si>
   <si>
@@ -1732,23 +1720,13 @@
   </si>
   <si>
     <t>plhcv_polaris</t>
-  </si>
-  <si>
-    <t>Tanzania</t>
-  </si>
-  <si>
-    <t>Russia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1758,13 +1736,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1804,38 +1775,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1873,7 +1833,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1907,7 +1867,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1942,10 +1901,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2118,11 +2076,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2154,7 +2112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2186,7 +2144,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2218,7 +2176,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2250,7 +2208,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2282,7 +2240,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2314,7 +2272,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2346,7 +2304,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2378,7 +2336,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2410,7 +2368,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2442,7 +2400,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2474,7 +2432,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2506,7 +2464,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2538,7 +2496,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2570,7 +2528,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2602,7 +2560,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2634,7 +2592,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2666,7 +2624,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2698,7 +2656,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2730,7 +2688,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2762,7 +2720,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2794,7 +2752,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2826,7 +2784,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2858,7 +2816,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2890,7 +2848,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2922,7 +2880,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2954,7 +2912,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2986,7 +2944,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -3018,7 +2976,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -3050,7 +3008,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -3082,7 +3040,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3114,7 +3072,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -3146,7 +3104,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -3178,7 +3136,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -3210,7 +3168,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -3248,11 +3206,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3278,7 +3236,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3295,16 +3253,16 @@
         <v>423</v>
       </c>
       <c r="F2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H2" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3321,16 +3279,16 @@
         <v>424</v>
       </c>
       <c r="F3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H3" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3347,16 +3305,16 @@
         <v>425</v>
       </c>
       <c r="F4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H4" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3373,16 +3331,16 @@
         <v>426</v>
       </c>
       <c r="F5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -3396,19 +3354,19 @@
         <v>394</v>
       </c>
       <c r="E6" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="F6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H6" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3422,19 +3380,19 @@
         <v>395</v>
       </c>
       <c r="E7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G7" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3448,19 +3406,19 @@
         <v>396</v>
       </c>
       <c r="E8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H8" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3474,19 +3432,19 @@
         <v>397</v>
       </c>
       <c r="E9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G9" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H9" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3500,19 +3458,19 @@
         <v>398</v>
       </c>
       <c r="E10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G10" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H10" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3526,19 +3484,19 @@
         <v>399</v>
       </c>
       <c r="E11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -3552,19 +3510,19 @@
         <v>400</v>
       </c>
       <c r="E12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F12" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H12" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3578,19 +3536,19 @@
         <v>401</v>
       </c>
       <c r="E13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G13" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H13" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -3604,19 +3562,19 @@
         <v>394</v>
       </c>
       <c r="E14" t="s">
-        <v>435</v>
+        <v>394</v>
       </c>
       <c r="F14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H14" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -3630,19 +3588,19 @@
         <v>402</v>
       </c>
       <c r="E15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F15" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G15" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H15" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -3656,19 +3614,19 @@
         <v>403</v>
       </c>
       <c r="E16" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G16" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H16" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -3682,19 +3640,19 @@
         <v>404</v>
       </c>
       <c r="E17" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F17" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H17" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -3708,19 +3666,19 @@
         <v>405</v>
       </c>
       <c r="E18" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F18" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G18" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H18" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -3734,19 +3692,19 @@
         <v>406</v>
       </c>
       <c r="E19" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F19" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G19" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H19" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3760,19 +3718,19 @@
         <v>407</v>
       </c>
       <c r="E20" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F20" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G20" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H20" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -3786,19 +3744,19 @@
         <v>408</v>
       </c>
       <c r="E21" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F21" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G21" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H21" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -3812,19 +3770,19 @@
         <v>409</v>
       </c>
       <c r="E22" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F22" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G22" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H22" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -3838,19 +3796,19 @@
         <v>410</v>
       </c>
       <c r="E23" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F23" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G23" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H23" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3864,19 +3822,19 @@
         <v>411</v>
       </c>
       <c r="E24" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F24" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G24" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H24" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3890,19 +3848,19 @@
         <v>412</v>
       </c>
       <c r="E25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F25" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G25" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H25" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -3916,19 +3874,19 @@
         <v>413</v>
       </c>
       <c r="E26" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F26" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G26" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H26" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -3942,19 +3900,19 @@
         <v>414</v>
       </c>
       <c r="E27" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F27" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G27" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H27" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -3968,19 +3926,19 @@
         <v>415</v>
       </c>
       <c r="E28" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F28" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G28" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H28" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -3994,19 +3952,19 @@
         <v>416</v>
       </c>
       <c r="E29" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F29" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G29" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H29" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -4020,19 +3978,19 @@
         <v>417</v>
       </c>
       <c r="E30" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F30" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G30" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H30" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -4046,19 +4004,19 @@
         <v>418</v>
       </c>
       <c r="E31" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F31" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G31" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H31" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -4072,19 +4030,19 @@
         <v>419</v>
       </c>
       <c r="E32" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F32" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G32" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H32" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -4098,19 +4056,19 @@
         <v>420</v>
       </c>
       <c r="E33" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F33" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G33" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H33" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -4124,19 +4082,19 @@
         <v>421</v>
       </c>
       <c r="E34" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F34" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G34" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H34" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -4150,16 +4108,16 @@
         <v>422</v>
       </c>
       <c r="E35" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F35" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G35" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H35" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -4168,222 +4126,206 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2">
-        <v>7280.8673036708769</v>
+        <v>7280.867303670877</v>
       </c>
       <c r="C2">
-        <v>6710.2379755218926</v>
+        <v>6710.237975521893</v>
       </c>
       <c r="D2">
-        <v>7935.2517378400762</v>
+        <v>7935.251737840076</v>
       </c>
       <c r="E2">
         <v>9708</v>
       </c>
       <c r="F2">
-        <v>6347.6643396848558</v>
+        <v>6347.664339684856</v>
       </c>
       <c r="G2">
         <v>718826.8159282289</v>
       </c>
       <c r="H2">
-        <v>589855.31825169292</v>
+        <v>589855.3182516929</v>
       </c>
       <c r="I2">
-        <v>794749.25134992111</v>
+        <v>794749.2513499211</v>
       </c>
       <c r="J2">
         <v>484523</v>
       </c>
       <c r="K2">
-        <v>497046.33899999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>497046.339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2749.8249487657872</v>
+        <v>2749.824948765787</v>
       </c>
       <c r="C3">
-        <v>2361.3531898553329</v>
+        <v>2361.353189855333</v>
       </c>
       <c r="D3">
-        <v>3091.1823009713671</v>
+        <v>3091.182300971367</v>
       </c>
       <c r="E3">
         <v>3416</v>
       </c>
       <c r="F3">
-        <v>2710.7458820736601</v>
+        <v>2710.74588207366</v>
       </c>
       <c r="G3">
-        <v>123764.46439141979</v>
+        <v>123764.4643914198</v>
       </c>
       <c r="H3">
-        <v>115191.79385503269</v>
+        <v>115191.7938550327</v>
       </c>
       <c r="I3">
-        <v>135175.19387853611</v>
+        <v>135175.1938785361</v>
       </c>
       <c r="J3">
         <v>125566</v>
       </c>
       <c r="K3">
-        <v>123329.94899999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>123329.949</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>102325.54151818321</v>
+        <v>102325.5415181832</v>
       </c>
       <c r="C4">
         <v>101187.8878252836</v>
       </c>
       <c r="D4">
-        <v>103402.60643364119</v>
+        <v>103402.6064336412</v>
       </c>
       <c r="E4">
         <v>110000</v>
       </c>
       <c r="F4">
-        <v>91160.424626460997</v>
+        <v>91160.424626461</v>
       </c>
       <c r="G4">
-        <v>9672416.7356810197</v>
+        <v>9672416.73568102</v>
       </c>
       <c r="H4">
-        <v>9464170.6502658818</v>
+        <v>9464170.650265882</v>
       </c>
       <c r="I4">
-        <v>9918636.1199967805</v>
+        <v>9918636.119996781</v>
       </c>
       <c r="J4">
         <v>8790812</v>
       </c>
       <c r="K4">
-        <v>9548390.1830000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9548390.183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5">
-        <v>19908.942184373329</v>
+        <v>19908.94218437333</v>
       </c>
       <c r="C5">
-        <v>19830.094293156661</v>
+        <v>19830.09429315666</v>
       </c>
       <c r="D5">
-        <v>19995.223739668119</v>
+        <v>19995.22373966812</v>
       </c>
       <c r="E5">
         <v>11876</v>
       </c>
       <c r="F5">
-        <v>3872.2232275925221</v>
+        <v>3872.223227592522</v>
       </c>
       <c r="G5">
-        <v>539554.52515908517</v>
+        <v>539554.5251590852</v>
       </c>
       <c r="H5">
-        <v>528034.76012723451</v>
+        <v>528034.7601272345</v>
       </c>
       <c r="I5">
-        <v>553609.64068704064</v>
+        <v>553609.6406870406</v>
       </c>
       <c r="J5">
         <v>511036</v>
       </c>
       <c r="K5">
-        <v>548666.43299999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>548666.433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6">
-        <v>7531.1308063653287</v>
+        <v>7531.130806365329</v>
       </c>
       <c r="C6">
-        <v>7367.1071038952596</v>
+        <v>7367.10710389526</v>
       </c>
       <c r="D6">
         <v>7699.600666635034</v>
       </c>
-      <c r="F6" s="2">
-        <v>3499.1267815073029</v>
-      </c>
       <c r="G6">
-        <v>297090.00929125748</v>
+        <v>297090.0092912575</v>
       </c>
       <c r="H6">
-        <v>289688.29910982051</v>
+        <v>289688.2991098205</v>
       </c>
       <c r="I6">
-        <v>307929.97464857588</v>
+        <v>307929.9746485759</v>
       </c>
       <c r="J6">
         <v>257189</v>
@@ -4392,77 +4334,77 @@
         <v>288535.63</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7">
-        <v>5420.7376280820254</v>
+        <v>5420.737628082025</v>
       </c>
       <c r="C7">
-        <v>5174.2204663141029</v>
+        <v>5174.220466314103</v>
       </c>
       <c r="D7">
-        <v>5551.5042440684019</v>
+        <v>5551.504244068402</v>
       </c>
       <c r="E7">
         <v>3725</v>
       </c>
       <c r="F7">
-        <v>3252.7759750944442</v>
+        <v>3252.775975094444</v>
       </c>
       <c r="G7">
-        <v>160500.53799627331</v>
+        <v>160500.5379962733</v>
       </c>
       <c r="H7">
-        <v>155007.05789939829</v>
+        <v>155007.0578993983</v>
       </c>
       <c r="I7">
-        <v>167653.91714506171</v>
+        <v>167653.9171450617</v>
       </c>
       <c r="J7">
         <v>157542</v>
       </c>
       <c r="K7">
-        <v>153157.01699999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>153157.017</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8">
-        <v>15871.898584528941</v>
+        <v>15871.89858452894</v>
       </c>
       <c r="C8">
         <v>15687.93455040289</v>
       </c>
       <c r="D8">
-        <v>16172.212835775939</v>
+        <v>16172.21283577594</v>
       </c>
       <c r="E8">
         <v>13104</v>
       </c>
       <c r="F8">
-        <v>8857.4218787569771</v>
+        <v>8857.421878756977</v>
       </c>
       <c r="G8">
-        <v>423082.76519872242</v>
+        <v>423082.7651987224</v>
       </c>
       <c r="H8">
-        <v>401752.75598749903</v>
+        <v>401752.755987499</v>
       </c>
       <c r="I8">
-        <v>458301.77766802511</v>
+        <v>458301.7776680251</v>
       </c>
       <c r="J8">
         <v>432499</v>
       </c>
       <c r="K8">
-        <v>423682.91899999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>423682.919</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -4470,10 +4412,10 @@
         <v>16770.73423807279</v>
       </c>
       <c r="C9">
-        <v>15478.361088406469</v>
+        <v>15478.36108840647</v>
       </c>
       <c r="D9">
-        <v>18006.804412826419</v>
+        <v>18006.80441282642</v>
       </c>
       <c r="E9">
         <v>13490</v>
@@ -4482,22 +4424,22 @@
         <v>13681.63625619575</v>
       </c>
       <c r="G9">
-        <v>695834.96974295704</v>
+        <v>695834.969742957</v>
       </c>
       <c r="H9">
-        <v>670260.91207404714</v>
+        <v>670260.9120740471</v>
       </c>
       <c r="I9">
-        <v>726090.86302173301</v>
+        <v>726090.863021733</v>
       </c>
       <c r="J9">
         <v>691928</v>
       </c>
       <c r="K9">
-        <v>697035.19400000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>697035.194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4505,7 +4447,7 @@
         <v>10755.0155219854</v>
       </c>
       <c r="C10">
-        <v>10622.884976505569</v>
+        <v>10622.88497650557</v>
       </c>
       <c r="D10">
         <v>10898.96375281232</v>
@@ -4514,48 +4456,48 @@
         <v>10714</v>
       </c>
       <c r="F10">
-        <v>9144.5074542684069</v>
+        <v>9144.507454268407</v>
       </c>
       <c r="G10">
-        <v>448057.19791146711</v>
+        <v>448057.1979114671</v>
       </c>
       <c r="H10">
-        <v>441285.75223103538</v>
+        <v>441285.7522310354</v>
       </c>
       <c r="I10">
-        <v>456693.31708489789</v>
+        <v>456693.3170848979</v>
       </c>
       <c r="J10">
         <v>442797</v>
       </c>
       <c r="K10">
-        <v>455797.49900000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>455797.499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11">
-        <v>44370.109729529497</v>
+        <v>44370.1097295295</v>
       </c>
       <c r="C11">
-        <v>43204.824747758721</v>
+        <v>43204.82474775872</v>
       </c>
       <c r="D11">
-        <v>45263.750843019057</v>
+        <v>45263.75084301906</v>
       </c>
       <c r="E11">
         <v>27596</v>
       </c>
       <c r="F11">
-        <v>25651.533755058121</v>
+        <v>25651.53375505812</v>
       </c>
       <c r="G11">
         <v>1446386.222586907</v>
       </c>
       <c r="H11">
-        <v>1412524.7258614809</v>
+        <v>1412524.725861481</v>
       </c>
       <c r="I11">
         <v>1483522.108888485</v>
@@ -4564,21 +4506,21 @@
         <v>1349056</v>
       </c>
       <c r="K11">
-        <v>1430474.5360000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1430474.536</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12">
-        <v>6916.1245218825206</v>
+        <v>6916.124521882521</v>
       </c>
       <c r="C12">
-        <v>6250.0225564034217</v>
+        <v>6250.022556403422</v>
       </c>
       <c r="D12">
-        <v>7270.4580171387897</v>
+        <v>7270.45801713879</v>
       </c>
       <c r="E12">
         <v>3352</v>
@@ -4593,18 +4535,18 @@
         <v>117221.715590786</v>
       </c>
       <c r="I12">
-        <v>132389.02185720031</v>
+        <v>132389.0218572003</v>
       </c>
       <c r="J12">
         <v>62170</v>
       </c>
       <c r="K12">
-        <v>124146.19100000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>124146.191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>570</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>1243.56846085597</v>
@@ -4613,46 +4555,43 @@
         <v>1131.995102142683</v>
       </c>
       <c r="D13">
-        <v>1356.2740654576739</v>
+        <v>1356.274065457674</v>
       </c>
       <c r="E13">
         <v>1312</v>
       </c>
       <c r="F13">
-        <v>784.15714385129149</v>
+        <v>784.1571438512915</v>
       </c>
       <c r="G13">
-        <v>98567.212504191149</v>
+        <v>98567.21250419115</v>
       </c>
       <c r="H13">
-        <v>92799.971861178594</v>
+        <v>92799.97186117859</v>
       </c>
       <c r="I13">
-        <v>106407.63966967769</v>
+        <v>106407.6396696777</v>
       </c>
       <c r="J13">
         <v>99576</v>
       </c>
       <c r="K13">
-        <v>100030.04399999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100030.044</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14">
-        <v>13343.762409512839</v>
+        <v>13343.76240951284</v>
       </c>
       <c r="C14">
-        <v>13135.562051529059</v>
+        <v>13135.56205152906</v>
       </c>
       <c r="D14">
         <v>13559.61930677135</v>
       </c>
-      <c r="F14" s="2">
-        <v>2878.675780504404</v>
-      </c>
       <c r="G14">
         <v>341848.6001001742</v>
       </c>
@@ -4660,7 +4599,7 @@
         <v>335269.9354314566</v>
       </c>
       <c r="I14">
-        <v>349901.12385450158</v>
+        <v>349901.1238545016</v>
       </c>
       <c r="J14">
         <v>356043</v>
@@ -4669,15 +4608,15 @@
         <v>345238.89</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15">
-        <v>14192.690274142509</v>
+        <v>14192.69027414251</v>
       </c>
       <c r="C15">
-        <v>13838.418349587069</v>
+        <v>13838.41834958707</v>
       </c>
       <c r="D15">
         <v>14563.27217929379</v>
@@ -4686,48 +4625,48 @@
         <v>3159</v>
       </c>
       <c r="F15">
-        <v>13875.910012010359</v>
+        <v>13875.91001201036</v>
       </c>
       <c r="G15">
-        <v>911212.03212246415</v>
+        <v>911212.0321224642</v>
       </c>
       <c r="H15">
-        <v>901234.51931808714</v>
+        <v>901234.5193180871</v>
       </c>
       <c r="I15">
-        <v>925582.05378447368</v>
+        <v>925582.0537844737</v>
       </c>
       <c r="J15">
         <v>243978</v>
       </c>
       <c r="K15">
-        <v>943161.54500000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>943161.545</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16">
-        <v>5148.8306410432524</v>
+        <v>5148.830641043252</v>
       </c>
       <c r="C16">
-        <v>4653.5145149235523</v>
+        <v>4653.514514923552</v>
       </c>
       <c r="D16">
-        <v>5652.2929959032926</v>
+        <v>5652.292995903293</v>
       </c>
       <c r="E16">
-        <v>56.921752499999997</v>
+        <v>56.9217525</v>
       </c>
       <c r="F16">
-        <v>3157.1557912445091</v>
+        <v>3157.155791244509</v>
       </c>
       <c r="G16">
-        <v>103621.07418351321</v>
+        <v>103621.0741835132</v>
       </c>
       <c r="H16">
-        <v>98799.167875778454</v>
+        <v>98799.16787577845</v>
       </c>
       <c r="I16">
         <v>109363.3237972362</v>
@@ -4736,21 +4675,21 @@
         <v>48600</v>
       </c>
       <c r="K16">
-        <v>87553.732000000004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>87553.732</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="B17">
-        <v>6037.6666207905209</v>
+        <v>6037.666620790521</v>
       </c>
       <c r="C17">
-        <v>6008.4505936048054</v>
+        <v>6008.450593604805</v>
       </c>
       <c r="D17">
-        <v>6059.9719893127476</v>
+        <v>6059.971989312748</v>
       </c>
       <c r="E17">
         <v>4103</v>
@@ -4759,48 +4698,48 @@
         <v>3052.982349656902</v>
       </c>
       <c r="G17">
-        <v>164679.90693937329</v>
+        <v>164679.9069393733</v>
       </c>
       <c r="H17">
         <v>161509.9607970345</v>
       </c>
       <c r="I17">
-        <v>168299.71838352291</v>
+        <v>168299.7183835229</v>
       </c>
       <c r="J17">
         <v>170824</v>
       </c>
       <c r="K17">
-        <v>165921.35500000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>165921.355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>26</v>
       </c>
       <c r="B18">
-        <v>2183.3114319249012</v>
+        <v>2183.311431924901</v>
       </c>
       <c r="C18">
-        <v>2142.9850394066511</v>
+        <v>2142.985039406651</v>
       </c>
       <c r="D18">
-        <v>2233.1265292229091</v>
+        <v>2233.126529222909</v>
       </c>
       <c r="E18">
         <v>1626</v>
       </c>
       <c r="F18">
-        <v>2617.6002212906542</v>
+        <v>2617.600221290654</v>
       </c>
       <c r="G18">
-        <v>55316.014826579689</v>
+        <v>55316.01482657969</v>
       </c>
       <c r="H18">
-        <v>52413.811492465153</v>
+        <v>52413.81149246515</v>
       </c>
       <c r="I18">
-        <v>59480.169050997218</v>
+        <v>59480.16905099722</v>
       </c>
       <c r="J18">
         <v>73675</v>
@@ -4809,42 +4748,42 @@
         <v>58914.76</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>571</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>75340.61735174671</v>
       </c>
       <c r="C19">
-        <v>73530.326468014275</v>
+        <v>73530.32646801427</v>
       </c>
       <c r="D19">
-        <v>77385.825764661175</v>
+        <v>77385.82576466117</v>
       </c>
       <c r="E19">
         <v>33877</v>
       </c>
       <c r="F19">
-        <v>79840.238970237377</v>
+        <v>79840.23897023738</v>
       </c>
       <c r="G19">
-        <v>2670196.5022321111</v>
+        <v>2670196.502232111</v>
       </c>
       <c r="H19">
-        <v>2615003.5900278878</v>
+        <v>2615003.590027888</v>
       </c>
       <c r="I19">
-        <v>2741391.8178157271</v>
+        <v>2741391.817815727</v>
       </c>
       <c r="J19">
         <v>2663597</v>
       </c>
       <c r="K19">
-        <v>2731434.8739999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2731434.874</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -4852,16 +4791,16 @@
         <v>31403.98982057305</v>
       </c>
       <c r="C20">
-        <v>31266.810449700391</v>
+        <v>31266.81044970039</v>
       </c>
       <c r="D20">
-        <v>31562.946721252851</v>
+        <v>31562.94672125285</v>
       </c>
       <c r="E20">
         <v>18031</v>
       </c>
       <c r="F20">
-        <v>17359.049301855881</v>
+        <v>17359.04930185588</v>
       </c>
       <c r="G20">
         <v>1221423.09252899</v>
@@ -4876,62 +4815,62 @@
         <v>1250706</v>
       </c>
       <c r="K20">
-        <v>1334368.7919999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1334368.792</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="B21">
-        <v>9611.8008930920405</v>
+        <v>9611.80089309204</v>
       </c>
       <c r="C21">
-        <v>9291.6220973565523</v>
+        <v>9291.622097356552</v>
       </c>
       <c r="D21">
-        <v>9970.7216008578689</v>
+        <v>9970.721600857869</v>
       </c>
       <c r="E21">
         <v>35598</v>
       </c>
       <c r="F21">
-        <v>2310.2900259805751</v>
+        <v>2310.290025980575</v>
       </c>
       <c r="G21">
-        <v>378613.42712182843</v>
+        <v>378613.4271218284</v>
       </c>
       <c r="H21">
-        <v>362227.59627555829</v>
+        <v>362227.5962755583</v>
       </c>
       <c r="I21">
-        <v>400273.78657320951</v>
+        <v>400273.7865732095</v>
       </c>
       <c r="J21">
         <v>1065843</v>
       </c>
       <c r="K21">
-        <v>372758.82400000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>372758.824</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>30</v>
       </c>
       <c r="B22">
-        <v>7259.9151992671923</v>
+        <v>7259.915199267192</v>
       </c>
       <c r="C22">
         <v>6038.174824066401</v>
       </c>
       <c r="D22">
-        <v>8465.0981774083175</v>
+        <v>8465.098177408317</v>
       </c>
       <c r="E22">
         <v>4028</v>
       </c>
       <c r="F22">
-        <v>3335.1380416622219</v>
+        <v>3335.138041662222</v>
       </c>
       <c r="G22">
         <v>541862.7040843576</v>
@@ -4940,42 +4879,42 @@
         <v>507827.0341544621</v>
       </c>
       <c r="I22">
-        <v>592974.11143633595</v>
+        <v>592974.111436336</v>
       </c>
       <c r="J22">
         <v>535868</v>
       </c>
       <c r="K22">
-        <v>604522.36100000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>604522.361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>31</v>
       </c>
       <c r="B23">
-        <v>4916.6616858224334</v>
+        <v>4916.661685822433</v>
       </c>
       <c r="C23">
-        <v>4773.6107167219461</v>
+        <v>4773.610716721946</v>
       </c>
       <c r="D23">
-        <v>5030.0015064374147</v>
+        <v>5030.001506437415</v>
       </c>
       <c r="E23">
         <v>3646</v>
       </c>
       <c r="F23">
-        <v>3409.7012892062021</v>
+        <v>3409.701289206202</v>
       </c>
       <c r="G23">
-        <v>315355.88013524428</v>
+        <v>315355.8801352443</v>
       </c>
       <c r="H23">
-        <v>310966.70046724391</v>
+        <v>310966.7004672439</v>
       </c>
       <c r="I23">
-        <v>320936.90186696051</v>
+        <v>320936.9018669605</v>
       </c>
       <c r="J23">
         <v>309159</v>
@@ -4984,15 +4923,15 @@
         <v>309514.745</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>32</v>
       </c>
       <c r="B24">
-        <v>17297.725959583269</v>
+        <v>17297.72595958327</v>
       </c>
       <c r="C24">
-        <v>17118.837928631889</v>
+        <v>17118.83792863189</v>
       </c>
       <c r="D24">
         <v>17482.6599131892</v>
@@ -5001,33 +4940,33 @@
         <v>5736</v>
       </c>
       <c r="F24">
-        <v>4959.7965673442277</v>
+        <v>4959.796567344228</v>
       </c>
       <c r="G24">
-        <v>655480.59246754646</v>
+        <v>655480.5924675465</v>
       </c>
       <c r="H24">
-        <v>623738.58351311996</v>
+        <v>623738.58351312</v>
       </c>
       <c r="I24">
-        <v>710939.68939141219</v>
+        <v>710939.6893914122</v>
       </c>
       <c r="J24">
         <v>678258</v>
       </c>
       <c r="K24">
-        <v>688835.49899999995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>688835.499</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25">
-        <v>1177.7815716868331</v>
+        <v>1177.781571686833</v>
       </c>
       <c r="C25">
-        <v>1097.2355307227431</v>
+        <v>1097.235530722743</v>
       </c>
       <c r="D25">
         <v>1248.836339147623</v>
@@ -5036,45 +4975,45 @@
         <v>814</v>
       </c>
       <c r="F25">
-        <v>788.54191318027972</v>
+        <v>788.5419131802797</v>
       </c>
       <c r="G25">
-        <v>56138.758429250913</v>
+        <v>56138.75842925091</v>
       </c>
       <c r="H25">
-        <v>54762.365888864893</v>
+        <v>54762.36588886489</v>
       </c>
       <c r="I25">
-        <v>57881.228384955983</v>
+        <v>57881.22838495598</v>
       </c>
       <c r="J25">
         <v>57756</v>
       </c>
       <c r="K25">
-        <v>55881.142999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>55881.143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>34</v>
       </c>
       <c r="B26">
-        <v>52509.609893623747</v>
+        <v>52509.60989362375</v>
       </c>
       <c r="C26">
-        <v>44892.739183971258</v>
+        <v>44892.73918397126</v>
       </c>
       <c r="D26">
-        <v>60360.835627573862</v>
+        <v>60360.83562757386</v>
       </c>
       <c r="E26">
         <v>53383</v>
       </c>
       <c r="F26">
-        <v>52206.336490641297</v>
+        <v>52206.3364906413</v>
       </c>
       <c r="G26">
-        <v>4114015.2358521651</v>
+        <v>4114015.235852165</v>
       </c>
       <c r="H26">
         <v>3922419.76601246</v>
@@ -5086,18 +5025,18 @@
         <v>4012657</v>
       </c>
       <c r="K26">
-        <v>4234853.6050000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4234853.605</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="B27">
-        <v>5347.9771179979971</v>
+        <v>5347.977117997997</v>
       </c>
       <c r="C27">
-        <v>5269.7143545057588</v>
+        <v>5269.714354505759</v>
       </c>
       <c r="D27">
         <v>5433.513199991844</v>
@@ -5106,16 +5045,16 @@
         <v>4625</v>
       </c>
       <c r="F27">
-        <v>4713.1198725910244</v>
+        <v>4713.119872591024</v>
       </c>
       <c r="G27">
-        <v>184592.01447204041</v>
+        <v>184592.0144720404</v>
       </c>
       <c r="H27">
-        <v>178486.49164033731</v>
+        <v>178486.4916403373</v>
       </c>
       <c r="I27">
-        <v>193269.04965112641</v>
+        <v>193269.0496511264</v>
       </c>
       <c r="J27">
         <v>183160</v>
@@ -5124,18 +5063,18 @@
         <v>184345.875</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28">
-        <v>3853.9070943707302</v>
+        <v>3853.90709437073</v>
       </c>
       <c r="C28">
-        <v>3823.1516518694912</v>
+        <v>3823.151651869491</v>
       </c>
       <c r="D28">
-        <v>3896.7968461294381</v>
+        <v>3896.796846129438</v>
       </c>
       <c r="E28">
         <v>1939</v>
@@ -5144,13 +5083,13 @@
         <v>1731.287072280378</v>
       </c>
       <c r="G28">
-        <v>128483.10577379281</v>
+        <v>128483.1057737928</v>
       </c>
       <c r="H28">
         <v>121376.0605498339</v>
       </c>
       <c r="I28">
-        <v>134854.05493130139</v>
+        <v>134854.0549313014</v>
       </c>
       <c r="J28">
         <v>128501</v>
@@ -5159,15 +5098,15 @@
         <v>130544.675</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="B29">
-        <v>10264.562335256151</v>
+        <v>10264.56233525615</v>
       </c>
       <c r="C29">
-        <v>10017.029490027749</v>
+        <v>10017.02949002775</v>
       </c>
       <c r="D29">
         <v>10567.12957677383</v>
@@ -5176,30 +5115,30 @@
         <v>8939</v>
       </c>
       <c r="F29">
-        <v>10103.430472462151</v>
+        <v>10103.43047246215</v>
       </c>
       <c r="G29">
-        <v>444954.39693336398</v>
+        <v>444954.396933364</v>
       </c>
       <c r="H29">
         <v>434321.7312553958</v>
       </c>
       <c r="I29">
-        <v>461349.81470487191</v>
+        <v>461349.8147048719</v>
       </c>
       <c r="J29">
         <v>427470</v>
       </c>
       <c r="K29">
-        <v>438389.04200000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>438389.042</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30">
-        <v>18709.013787832959</v>
+        <v>18709.01378783296</v>
       </c>
       <c r="C30">
         <v>17477.08664423721</v>
@@ -5214,13 +5153,13 @@
         <v>14863.57602627603</v>
       </c>
       <c r="G30">
-        <v>922069.41668523813</v>
+        <v>922069.4166852381</v>
       </c>
       <c r="H30">
-        <v>903595.41795866902</v>
+        <v>903595.417958669</v>
       </c>
       <c r="I30">
-        <v>956745.46244651719</v>
+        <v>956745.4624465172</v>
       </c>
       <c r="J30">
         <v>890997</v>
@@ -5229,68 +5168,68 @@
         <v>916385.86</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
         <v>39</v>
       </c>
       <c r="B31">
-        <v>82.425313325648318</v>
+        <v>82.42531332564832</v>
       </c>
       <c r="C31">
-        <v>80.859931351021558</v>
+        <v>80.85993135102156</v>
       </c>
       <c r="D31">
-        <v>84.477713599401554</v>
+        <v>84.47771359940155</v>
       </c>
       <c r="E31">
         <v>85</v>
       </c>
       <c r="F31">
-        <v>84.267373396876778</v>
+        <v>84.26737339687678</v>
       </c>
       <c r="G31">
-        <v>3304.5695859198208</v>
+        <v>3304.569585919821</v>
       </c>
       <c r="H31">
-        <v>2550.1150963709879</v>
+        <v>2550.115096370988</v>
       </c>
       <c r="I31">
-        <v>3399.4338920859468</v>
+        <v>3399.433892085947</v>
       </c>
       <c r="J31">
         <v>3048</v>
       </c>
       <c r="K31">
-        <v>3405.8310000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3405.831</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>40</v>
       </c>
       <c r="B32">
-        <v>36912.093041511907</v>
+        <v>36912.09304151191</v>
       </c>
       <c r="C32">
-        <v>36288.211089499047</v>
+        <v>36288.21108949905</v>
       </c>
       <c r="D32">
-        <v>37672.532355048388</v>
+        <v>37672.53235504839</v>
       </c>
       <c r="E32">
         <v>17008</v>
       </c>
       <c r="F32">
-        <v>19638.531746652141</v>
+        <v>19638.53174665214</v>
       </c>
       <c r="G32">
         <v>1043396.319160552</v>
       </c>
       <c r="H32">
-        <v>1015164.7521192289</v>
+        <v>1015164.752119229</v>
       </c>
       <c r="I32">
-        <v>1081138.6372456809</v>
+        <v>1081138.637245681</v>
       </c>
       <c r="J32">
         <v>1020178</v>
@@ -5299,18 +5238,18 @@
         <v>1060440.558</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>41</v>
       </c>
       <c r="B33">
-        <v>37911.601963780347</v>
+        <v>37911.60196378035</v>
       </c>
       <c r="C33">
-        <v>37195.866618795349</v>
+        <v>37195.86661879535</v>
       </c>
       <c r="D33">
-        <v>38497.872808708278</v>
+        <v>38497.87280870828</v>
       </c>
       <c r="E33">
         <v>39134</v>
@@ -5319,10 +5258,10 @@
         <v>29860.39764779399</v>
       </c>
       <c r="G33">
-        <v>1158501.4915723051</v>
+        <v>1158501.491572305</v>
       </c>
       <c r="H33">
-        <v>1092314.7333935511</v>
+        <v>1092314.733393551</v>
       </c>
       <c r="I33">
         <v>1269135.586232221</v>
@@ -5334,304 +5273,77 @@
         <v>1191958.709</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>42</v>
       </c>
       <c r="B34">
-        <v>163806.31090932409</v>
+        <v>163806.3109093241</v>
       </c>
       <c r="C34">
         <v>154497.8816652094</v>
       </c>
       <c r="D34">
-        <v>170335.56660627981</v>
+        <v>170335.5666062798</v>
       </c>
       <c r="E34">
         <v>144187</v>
       </c>
       <c r="F34">
-        <v>166180.89420641301</v>
+        <v>166180.894206413</v>
       </c>
       <c r="G34">
-        <v>6027484.2576593701</v>
+        <v>6027484.25765937</v>
       </c>
       <c r="H34">
-        <v>5782604.4161389703</v>
+        <v>5782604.41613897</v>
       </c>
       <c r="I34">
-        <v>6367645.1704743728</v>
+        <v>6367645.170474373</v>
       </c>
       <c r="J34">
         <v>5507793</v>
       </c>
       <c r="K34">
-        <v>6100119.7180000003</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6100119.718</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
         <v>43</v>
       </c>
       <c r="B35">
-        <v>9115.3022110499933</v>
+        <v>9115.302211049993</v>
       </c>
       <c r="C35">
-        <v>8743.3682092286417</v>
+        <v>8743.368209228642</v>
       </c>
       <c r="D35">
-        <v>9432.9881475468937</v>
+        <v>9432.988147546894</v>
       </c>
       <c r="E35">
         <v>6630</v>
       </c>
       <c r="F35">
-        <v>7437.8857770835521</v>
+        <v>7437.885777083552</v>
       </c>
       <c r="G35">
-        <v>404760.47789741622</v>
+        <v>404760.4778974162</v>
       </c>
       <c r="H35">
-        <v>390143.99778341473</v>
+        <v>390143.9977834147</v>
       </c>
       <c r="I35">
-        <v>427180.33271054731</v>
+        <v>427180.3327105473</v>
       </c>
       <c r="J35">
         <v>374514</v>
       </c>
       <c r="K35">
-        <v>413803.58100000001</v>
+        <v>413803.581</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ce90f198977bd0ea8ac85803c661b37d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d425e27b80396f31a5c1d00c1f67fb78" ns2:_="">
-    <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="460e4ad2-c64b-4f67-8552-094351f252e3" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9012861f-df9c-4ac0-92bd-da4c61c7cfda" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{415049F2-7C18-4A80-A1C6-27D28904CE09}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15190C99-FCFA-4614-A261-977189FE87D5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA326C75-1368-4F5B-9808-88169314AB18}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>